--- a/generated/sources/systems/marketing/PR_seeding_tracker_FW26.xlsx
+++ b/generated/sources/systems/marketing/PR_seeding_tracker_FW26.xlsx
@@ -250,58 +250,58 @@
     <t>Vogue Italia (editorial)</t>
   </si>
   <si>
-    <t>MAYA 999</t>
-  </si>
-  <si>
-    <t>MAIRE 034</t>
-  </si>
-  <si>
-    <t>MAIRE 999</t>
-  </si>
-  <si>
-    <t>MONTCLA 999</t>
-  </si>
-  <si>
-    <t>ILVARO 999</t>
-  </si>
-  <si>
-    <t>ILVARO 20D</t>
-  </si>
-  <si>
-    <t>AMBRINE 23R</t>
-  </si>
-  <si>
-    <t>ARNEB 999</t>
-  </si>
-  <si>
-    <t>HERMINE 999</t>
-  </si>
-  <si>
-    <t>POLARIS CAPE 999</t>
-  </si>
-  <si>
-    <t>POLARIS OVERSIZED 999</t>
-  </si>
-  <si>
-    <t>LOGO T-SHIRT 001</t>
-  </si>
-  <si>
-    <t>MONTGENEVRE 999</t>
-  </si>
-  <si>
-    <t>MAYA 742</t>
-  </si>
-  <si>
-    <t>BADY 999 x4</t>
-  </si>
-  <si>
-    <t>POLARIS BALACLAVA 999</t>
-  </si>
-  <si>
-    <t>ILVARO 510</t>
-  </si>
-  <si>
-    <t>ILVARO 510 x2</t>
+    <t>NOVA 999</t>
+  </si>
+  <si>
+    <t>AUREA 034</t>
+  </si>
+  <si>
+    <t>AUREA 999</t>
+  </si>
+  <si>
+    <t>MISTRAL 999</t>
+  </si>
+  <si>
+    <t>IRIDIA 999</t>
+  </si>
+  <si>
+    <t>IRIDIA 20D</t>
+  </si>
+  <si>
+    <t>AMALIA 23R</t>
+  </si>
+  <si>
+    <t>ARTEM 999</t>
+  </si>
+  <si>
+    <t>LIVIANA 999</t>
+  </si>
+  <si>
+    <t>ASTRA CAPE 999</t>
+  </si>
+  <si>
+    <t>ASTRA OVERSIZED 999</t>
+  </si>
+  <si>
+    <t>VLOGO T-SHIRT 001</t>
+  </si>
+  <si>
+    <t>MONTELUCE 999</t>
+  </si>
+  <si>
+    <t>NOVA 742</t>
+  </si>
+  <si>
+    <t>ARIA 999 x4</t>
+  </si>
+  <si>
+    <t>ASTRA BALACLAVA 999</t>
+  </si>
+  <si>
+    <t>IRIDIA 510</t>
+  </si>
+  <si>
+    <t>IRIDIA 510 x2</t>
   </si>
   <si>
     <t>4</t>
@@ -424,13 +424,13 @@
     <t>post date before sent date (sent through lounge, logged late)</t>
   </si>
   <si>
-    <t>for Paris FW wardrobe; NOT Ilvaro; Yoon Ha-eun NOT included (stylist pulled other brands)</t>
-  </si>
-  <si>
-    <t>no stock black Maire (DC 0)</t>
-  </si>
-  <si>
-    <t>PR Seoul 02/10 09:40 KST: photographed 01/10 outside PFW show in ILVARO powder pink. NOT in seeding list - own purchase / stylist. Organic. Contact agency for thank-you gifting.</t>
+    <t>for Paris FW wardrobe; NOT Iridia; Yoon Ha-eun NOT included (stylist pulled other brands)</t>
+  </si>
+  <si>
+    <t>no stock black Aurea (DC 0)</t>
+  </si>
+  <si>
+    <t>PR Seoul 02/10 09:40 KST: photographed 01/10 outside PFW show in IRIDIA powder pink. NOT in seeding list - own purchase / stylist. Organic. Contact agency for thank-you gifting.</t>
   </si>
   <si>
     <t>gifting request rejected by WMS HK30: ATP 0. retry after top-up 08/10</t>
